--- a/data/trans_camb/IP16A03-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16A03-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,06; 0,0</t>
+          <t>-14,91; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,88; 0,0</t>
+          <t>-14,73; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,46; 0,0</t>
+          <t>-14,33; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 13,7</t>
+          <t>-8,92; 14,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,98; 5,78</t>
+          <t>-11,06; 6,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,86; 11,47</t>
+          <t>-10,18; 11,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 6,09</t>
+          <t>-6,75; 6,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 1,52</t>
+          <t>-8,48; 1,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 3,78</t>
+          <t>-8,06; 4,07</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 561,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-16,77; -1,09</t>
+          <t>-17,51; -1,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-18,96; -4,25</t>
+          <t>-19,75; -4,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,66; -0,46</t>
+          <t>-18,17; -0,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,29; 3,42</t>
+          <t>-9,52; 2,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 5,45</t>
+          <t>-8,04; 5,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 5,28</t>
+          <t>-7,11; 6,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-11,28; -1,1</t>
+          <t>-11,44; -0,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,26; -0,85</t>
+          <t>-11,21; -0,96</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-9,72; 0,63</t>
+          <t>-9,35; 1,65</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 75,84</t>
+          <t>-100,0; 50,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 104,21</t>
+          <t>-100,0; 75,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1024,22 +1024,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-91,52; 554,82</t>
+          <t>-85,76; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 19,29</t>
+          <t>-100,0; 22,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 25,35</t>
+          <t>-100,0; 6,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-87,84; 26,42</t>
+          <t>-86,1; 65,4</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 18,11</t>
+          <t>-2,13; 18,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 10,83</t>
+          <t>-6,06; 11,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,0; 2,16</t>
+          <t>-10,35; 1,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,22; 6,19</t>
+          <t>-14,14; 5,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,01; 9,24</t>
+          <t>-12,01; 8,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,13; -0,33</t>
+          <t>-16,51; -0,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 8,29</t>
+          <t>-5,84; 9,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 6,53</t>
+          <t>-7,41; 6,33</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-11,41; -0,61</t>
+          <t>-11,97; -0,67</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-71,93; —</t>
+          <t>-53,84; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1230,32 +1230,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 244,44</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; 420,37</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-60,68; 276,7</t>
+          <t>-60,25; 328,21</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-80,63; 240,93</t>
+          <t>-83,36; 245,91</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-96,46; 56,28</t>
+          <t>-100,0; 0,66</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 9,03</t>
+          <t>-5,6; 9,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 4,34</t>
+          <t>-8,61; 4,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 5,14</t>
+          <t>-8,34; 5,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-20,04; -1,77</t>
+          <t>-20,34; -1,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-13,23; 9,53</t>
+          <t>-14,93; 9,8</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-18,3; 1,76</t>
+          <t>-19,15; 2,04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-11,53; 1,13</t>
+          <t>-11,31; 1,72</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-9,47; 4,28</t>
+          <t>-10,17; 4,32</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-11,08; 1,23</t>
+          <t>-12,52; 0,79</t>
         </is>
       </c>
     </row>
@@ -1451,27 +1451,27 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-82,64; 195,28</t>
+          <t>-86,58; 195,32</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 108,17</t>
+          <t>-100,0; 139,3</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-90,98; 58,41</t>
+          <t>-89,39; 65,76</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-84,7; 117,27</t>
+          <t>-84,97; 136,36</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 65,86</t>
+          <t>-100,0; 61,99</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 2,86</t>
+          <t>-5,49; 3,27</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,3; -0,57</t>
+          <t>-7,97; -0,52</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,28; -0,99</t>
+          <t>-8,24; -0,79</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,95; 0,97</t>
+          <t>-7,83; 1,14</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 1,96</t>
+          <t>-6,8; 3,05</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 0,07</t>
+          <t>-8,41; 0,14</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 0,59</t>
+          <t>-5,69; 0,45</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,15; -0,17</t>
+          <t>-6,49; -0,31</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,04; -1,42</t>
+          <t>-7,11; -1,59</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-69,25; 90,41</t>
+          <t>-68,85; 107,12</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-93,58; -1,78</t>
+          <t>-92,15; 0,77</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-94,44; -0,94</t>
+          <t>-93,67; -9,51</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-81,08; 34,68</t>
+          <t>-80,01; 44,86</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-75,28; 48,75</t>
+          <t>-70,34; 75,1</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-83,19; 10,49</t>
+          <t>-83,04; 7,25</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-64,06; 15,17</t>
+          <t>-66,01; 11,72</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-74,82; -2,17</t>
+          <t>-75,59; 2,93</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-82,26; -27,05</t>
+          <t>-82,41; -29,84</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A03-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16A03-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,91; 0,0</t>
+          <t>-13,95; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,73; 0,0</t>
+          <t>-12,4; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,33; 0,0</t>
+          <t>-13,95; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,92; 14,28</t>
+          <t>-7,1; 15,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,06; 6,15</t>
+          <t>-11,0; 5,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,18; 11,09</t>
+          <t>-10,07; 11,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 6,55</t>
+          <t>-5,8; 6,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 1,88</t>
+          <t>-8,79; 1,56</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 4,07</t>
+          <t>-7,64; 4,13</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 561,25</t>
+          <t>-100,0; 654,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-17,51; -1,1</t>
+          <t>-17,84; -1,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-19,75; -4,27</t>
+          <t>-19,66; -4,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-18,17; -0,57</t>
+          <t>-17,16; -0,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,52; 2,2</t>
+          <t>-9,42; 3,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 5,3</t>
+          <t>-7,63; 5,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 6,22</t>
+          <t>-7,4; 5,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-11,44; -0,76</t>
+          <t>-11,91; -1,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,21; -0,96</t>
+          <t>-11,35; -0,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-9,35; 1,65</t>
+          <t>-9,28; 0,76</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 50,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 75,89</t>
+          <t>-100,0; 130,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1024,22 +1024,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-85,76; —</t>
+          <t>-87,47; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 22,43</t>
+          <t>-100,0; 15,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 6,76</t>
+          <t>-100,0; 14,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-86,1; 65,4</t>
+          <t>-87,62; 31,71</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 18,9</t>
+          <t>-1,88; 18,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 11,51</t>
+          <t>-6,11; 12,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,35; 1,63</t>
+          <t>-11,23; 2,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-14,14; 5,33</t>
+          <t>-12,49; 5,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,01; 8,09</t>
+          <t>-12,58; 7,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,51; -0,27</t>
+          <t>-17,65; -0,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 9,1</t>
+          <t>-5,27; 9,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 6,33</t>
+          <t>-7,15; 6,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-11,97; -0,67</t>
+          <t>-11,35; -0,65</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-53,84; —</t>
+          <t>-61,05; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1230,12 +1230,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 244,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 420,37</t>
+          <t>-100,0; 467,56</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-60,25; 328,21</t>
+          <t>-57,25; 303,56</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-83,36; 245,91</t>
+          <t>-80,45; 265,82</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 0,66</t>
+          <t>-100,0; 19,61</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 9,29</t>
+          <t>-5,38; 10,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 4,25</t>
+          <t>-8,18; 4,48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,34; 5,13</t>
+          <t>-8,17; 5,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-20,34; -1,71</t>
+          <t>-20,16; -1,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-14,93; 9,8</t>
+          <t>-13,74; 9,59</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-19,15; 2,04</t>
+          <t>-18,34; 1,64</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-11,31; 1,72</t>
+          <t>-11,24; 1,67</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-10,17; 4,32</t>
+          <t>-10,05; 4,37</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-12,52; 0,79</t>
+          <t>-12,11; 1,39</t>
         </is>
       </c>
     </row>
@@ -1451,27 +1451,27 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-86,58; 195,32</t>
+          <t>-90,45; 218,75</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 139,3</t>
+          <t>-100,0; 113,82</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-89,39; 65,76</t>
+          <t>-91,29; 74,15</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-84,97; 136,36</t>
+          <t>-82,95; 135,79</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 61,99</t>
+          <t>-100,0; 58,57</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 3,27</t>
+          <t>-5,67; 3,06</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,97; -0,52</t>
+          <t>-8,09; -0,59</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,24; -0,79</t>
+          <t>-8,55; -1,1</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 1,14</t>
+          <t>-7,75; 1,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 3,05</t>
+          <t>-6,85; 2,38</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 0,14</t>
+          <t>-8,58; 0,01</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 0,45</t>
+          <t>-5,7; 0,55</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,49; -0,31</t>
+          <t>-5,98; -0,26</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,11; -1,59</t>
+          <t>-7,14; -1,6</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-68,85; 107,12</t>
+          <t>-68,07; 96,96</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-92,15; 0,77</t>
+          <t>-94,06; -2,0</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-93,67; -9,51</t>
+          <t>-93,9; -11,83</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-80,01; 44,86</t>
+          <t>-77,78; 29,58</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-70,34; 75,1</t>
+          <t>-70,59; 56,79</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-83,04; 7,25</t>
+          <t>-80,65; 9,86</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-66,01; 11,72</t>
+          <t>-67,46; 13,87</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-75,59; 2,93</t>
+          <t>-74,03; -0,06</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-82,41; -29,84</t>
+          <t>-82,06; -26,89</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A03-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16A03-Habitat-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos reconstituyentes como vitaminas, minerales, tónicos</t>
+          <t>Menores que consumieron medicamentos reconstituyentes como vitaminas, minerales, tónicos</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,34 +624,34 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,65</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-2,12</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-3,33</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-4,11</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-4,11</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>-4,11</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,65</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-2,12</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-0,88</t>
-        </is>
-      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>-0,53</t>
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-2,4</t>
+          <t>-3,72</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,95; 0,0</t>
+          <t>-7,64; 13,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,4; 0,0</t>
+          <t>-10,98; 5,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,95; 0,0</t>
+          <t>-15,79; 1,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 15,18</t>
+          <t>-14,06; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,0; 5,89</t>
+          <t>-15,88; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,07; 11,78</t>
+          <t>-14,46; 0,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 6,25</t>
+          <t>-6,62; 6,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,79; 1,56</t>
+          <t>-8,82; 1,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 4,13</t>
+          <t>-9,97; -0,36</t>
         </is>
       </c>
     </row>
@@ -730,34 +730,34 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>53,77%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-43,13%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-67,69%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>53,77%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-43,13%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-17,98%</t>
-        </is>
-      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t>-11,86%</t>
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-53,49%</t>
+          <t>-82,87%</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 654,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-2,99</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-1,24</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,1</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-8,4</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-10,22</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-8,1</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-2,99</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-1,24</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,2</t>
+          <t>-8,44</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-3,95</t>
+          <t>-3,85</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-17,84; -1,01</t>
+          <t>-9,29; 3,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-19,66; -4,3</t>
+          <t>-7,98; 5,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,16; -0,44</t>
+          <t>-7,2; 6,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,42; 3,28</t>
+          <t>-16,77; -1,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 5,85</t>
+          <t>-18,96; -4,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 5,83</t>
+          <t>-17,29; -1,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-11,91; -1,16</t>
+          <t>-11,28; -1,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,35; -0,79</t>
+          <t>-11,26; -0,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-9,28; 0,76</t>
+          <t>-9,76; 0,91</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-64,11%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-26,58%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-82,19%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-79,21%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-64,11%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-26,58%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-4,35%</t>
+          <t>-82,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-52,97%</t>
+          <t>-51,67%</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 130,34</t>
+          <t>-91,84; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 75,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1024,22 +1024,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-87,47; —</t>
+          <t>-100,0; 86,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 15,46</t>
+          <t>-100,0; 19,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 14,64</t>
+          <t>-100,0; 25,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-87,62; 31,71</t>
+          <t>-85,92; 42,66</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-2,73</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-2,69</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-6,28</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>7,22</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>2,17</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-2,36</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-2,73</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-2,69</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-6,49</t>
+          <t>-1,58</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-4,76</t>
+          <t>-4,27</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 18,7</t>
+          <t>-12,22; 6,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 12,1</t>
+          <t>-12,01; 9,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,23; 2,28</t>
+          <t>-18,03; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,49; 5,49</t>
+          <t>-2,32; 18,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,58; 7,43</t>
+          <t>-6,38; 10,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-17,65; -0,49</t>
+          <t>-9,53; 4,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 9,04</t>
+          <t>-5,47; 8,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 6,75</t>
+          <t>-7,56; 6,53</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-11,35; -0,65</t>
+          <t>-10,7; 0,41</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-34,05%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-33,61%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-78,38%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>185,09%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>55,53%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-60,48%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-34,05%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-33,61%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-80,97%</t>
+          <t>-40,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-75,63%</t>
+          <t>-67,87%</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-61,05; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1230,12 +1230,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-71,93; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 467,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-57,25; 303,56</t>
+          <t>-60,68; 276,7</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-80,45; 265,82</t>
+          <t>-80,63; 240,93</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 19,61</t>
+          <t>-95,36; 121,15</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-9,23</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-2,34</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-7,37</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>2,47</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-0,53</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,17</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-9,23</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-2,34</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-7,42</t>
+          <t>-0,1</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-4,62</t>
+          <t>-4,57</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 10,4</t>
+          <t>-20,04; -1,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 4,48</t>
+          <t>-13,23; 9,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 5,21</t>
+          <t>-18,29; 1,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-20,16; -1,58</t>
+          <t>-5,97; 9,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-13,74; 9,59</t>
+          <t>-8,46; 4,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-18,34; 1,64</t>
+          <t>-8,14; 5,25</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-11,24; 1,67</t>
+          <t>-11,53; 1,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-10,05; 4,37</t>
+          <t>-9,47; 4,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-12,11; 1,39</t>
+          <t>-11,09; 1,34</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-83,1%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-21,04%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-66,33%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>92,41%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-19,66%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-6,17%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-83,1%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-21,04%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-66,78%</t>
+          <t>-3,7%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-59,6%</t>
+          <t>-59,02%</t>
         </is>
       </c>
     </row>
@@ -1436,12 +1436,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-82,64; 195,28</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 107,73</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1451,27 +1451,27 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-90,45; 218,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 113,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-91,29; 74,15</t>
+          <t>-90,98; 58,41</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-82,95; 135,79</t>
+          <t>-84,7; 117,27</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 58,57</t>
+          <t>-100,0; 70,49</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-3,43</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-2,23</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-4,14</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-1,35</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-3,94</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-4,18</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-3,43</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-2,23</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-3,93</t>
+          <t>-3,99</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-4,1</t>
+          <t>-4,07</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 3,06</t>
+          <t>-7,95; 0,97</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,09; -0,59</t>
+          <t>-7,62; 1,96</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,55; -1,1</t>
+          <t>-8,83; -0,21</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 1,0</t>
+          <t>-5,81; 2,86</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 2,38</t>
+          <t>-8,3; -0,57</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 0,01</t>
+          <t>-7,88; -0,72</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 0,55</t>
+          <t>-5,39; 0,59</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,98; -0,26</t>
+          <t>-6,15; -0,17</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,14; -1,6</t>
+          <t>-7,02; -1,43</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-47,16%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-30,72%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-56,91%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-23,2%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-67,84%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-71,93%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-47,16%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-30,72%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-54,1%</t>
+          <t>-68,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-62,15%</t>
+          <t>-61,75%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-68,07; 96,96</t>
+          <t>-81,08; 34,68</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-94,06; -2,0</t>
+          <t>-75,28; 48,75</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-93,9; -11,83</t>
+          <t>-84,66; 3,0</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-77,78; 29,58</t>
+          <t>-69,25; 90,41</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-70,59; 56,79</t>
+          <t>-93,58; -1,78</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-80,65; 9,86</t>
+          <t>-93,91; 7,05</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-67,46; 13,87</t>
+          <t>-64,06; 15,17</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-74,03; -0,06</t>
+          <t>-74,82; -2,17</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-82,06; -26,89</t>
+          <t>-82,02; -21,23</t>
         </is>
       </c>
     </row>
